--- a/CLIENT RESOLU DU 19 au 25 01 2026 mod 01.xlsx
+++ b/CLIENT RESOLU DU 19 au 25 01 2026 mod 01.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\LENOVO\Desktop\BD ANALYSE\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C4B0FDD-FEF6-4BBF-BB9B-B7C825F9AE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13268DD5-730F-4155-A046-FE87D18F2000}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
